--- a/data/trans_orig/P04D$aparatos-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>453663</t>
+          <t>456935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>505052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>455001</t>
+          <t>454358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>504434</t>
+          <t>506555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>926848</t>
+          <t>926495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>996061</t>
+          <t>995012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,24%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>22841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>45473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153601</t>
+          <t>153609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>201010</t>
+          <t>201865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155522</t>
+          <t>153070</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>201816</t>
+          <t>199119</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>322679</t>
+          <t>320983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>387570</t>
+          <t>387663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43266</t>
+          <t>44116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>44250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75035</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>639145</t>
+          <t>640038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>701052</t>
+          <t>702082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674606</t>
+          <t>668838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>731411</t>
+          <t>731756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1329220</t>
+          <t>1332836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1420247</t>
+          <t>1420802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>49548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>50124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55255</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90570</t>
+          <t>91303</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248174</t>
+          <t>250790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>307775</t>
+          <t>308622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>232940</t>
+          <t>231993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>290533</t>
+          <t>288483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496008</t>
+          <t>494750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>582038</t>
+          <t>581371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44052</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45505</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46918</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>80556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>476592</t>
+          <t>476954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>534147</t>
+          <t>531972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533686</t>
+          <t>535024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584458</t>
+          <t>585855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1025297</t>
+          <t>1027207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1100350</t>
+          <t>1102251</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162753</t>
+          <t>163321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214770</t>
+          <t>215232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146909</t>
+          <t>144507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195621</t>
+          <t>192331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>326737</t>
+          <t>325612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394675</t>
+          <t>395221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41446</t>
+          <t>43592</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>76551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56993</t>
+          <t>57706</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>77655</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>118928</t>
+          <t>120776</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>470261</t>
+          <t>474538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>535729</t>
+          <t>534618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>536314</t>
+          <t>534351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>599680</t>
+          <t>598518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1025854</t>
+          <t>1031255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1121901</t>
+          <t>1122764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35608</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61569</t>
+          <t>62199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69340</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108033</t>
+          <t>107897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>342730</t>
+          <t>343509</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>407218</t>
+          <t>405238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>365611</t>
+          <t>365785</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>429211</t>
+          <t>429888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>722913</t>
+          <t>724989</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>815400</t>
+          <t>815516</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42926</t>
+          <t>42017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72774</t>
+          <t>71555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65405</t>
+          <t>64998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>100089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2104605</t>
+          <t>2104221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2219363</t>
+          <t>2220822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2250375</t>
+          <t>2252736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2369772</t>
+          <t>2368984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4390928</t>
+          <t>4389541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4557754</t>
+          <t>4560390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87160</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>130727</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>76675</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118292</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>177222</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>232053</t>
+          <t>234637</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>967788</t>
+          <t>961210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1074169</t>
+          <t>1074530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,39 +2797,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1005887</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>953120</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1056955</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>28,3%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1005887</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>953284</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1065229</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>26,82%</t>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1946023</t>
+          <t>1944460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2104058</t>
+          <t>2096331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117068</t>
+          <t>117374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167283</t>
+          <t>166824</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133591</t>
+          <t>135924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184342</t>
+          <t>184531</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269870</t>
+          <t>266958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>337742</t>
+          <t>339684</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>340734</t>
+          <t>341424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>391533</t>
+          <t>392956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>347192</t>
+          <t>348335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>400328</t>
+          <t>399230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>705409</t>
+          <t>703775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>777846</t>
+          <t>777360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>153765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199968</t>
+          <t>200644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148733</t>
+          <t>145216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>194224</t>
+          <t>189330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>313849</t>
+          <t>313275</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>375818</t>
+          <t>378484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105063</t>
+          <t>103879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146474</t>
+          <t>145631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95955</t>
+          <t>96742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135577</t>
+          <t>134848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>213544</t>
+          <t>211457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>268875</t>
+          <t>267855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>546854</t>
+          <t>547247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>614087</t>
+          <t>613713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557668</t>
+          <t>559630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>626887</t>
+          <t>627793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124112</t>
+          <t>1123973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1218893</t>
+          <t>1220698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24658</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35466</t>
+          <t>36047</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>247951</t>
+          <t>249542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>308210</t>
+          <t>310193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269113</t>
+          <t>273018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>330110</t>
+          <t>331400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>533821</t>
+          <t>536808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>620801</t>
+          <t>624469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128888</t>
+          <t>128412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>176575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122204</t>
+          <t>121947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169400</t>
+          <t>167439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261868</t>
+          <t>263652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329682</t>
+          <t>329692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>295562</t>
+          <t>298297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>351872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>294275</t>
+          <t>295737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>352163</t>
+          <t>352006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611157</t>
+          <t>611505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>692484</t>
+          <t>696488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>25263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43454</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234856</t>
+          <t>235915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292119</t>
+          <t>289304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266693</t>
+          <t>269339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322978</t>
+          <t>323206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>520640</t>
+          <t>518243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>597877</t>
+          <t>596674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131828</t>
+          <t>134562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>178358</t>
+          <t>181188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130625</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>176093</t>
+          <t>179656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>277090</t>
+          <t>276711</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341021</t>
+          <t>347597</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>497560</t>
+          <t>498689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>558538</t>
+          <t>557323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>530862</t>
+          <t>528911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>599813</t>
+          <t>598806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1049526</t>
+          <t>1048233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1139253</t>
+          <t>1142084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43801</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74059</t>
+          <t>73501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>86270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127952</t>
+          <t>127974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223718</t>
+          <t>225191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>276573</t>
+          <t>280113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>299351</t>
+          <t>300890</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>363135</t>
+          <t>364132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>540562</t>
+          <t>539956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622363</t>
+          <t>627982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81708</t>
+          <t>82254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>120507</t>
+          <t>122508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83706</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124148</t>
+          <t>123730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>176593</t>
+          <t>178325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232479</t>
+          <t>235450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1737791</t>
+          <t>1741456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1856233</t>
+          <t>1860158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1797706</t>
+          <t>1789234</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1912004</t>
+          <t>1913164</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3570685</t>
+          <t>3571319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3733500</t>
+          <t>3737823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76959</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>115788</t>
+          <t>116207</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107083</t>
+          <t>107476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157173</t>
+          <t>156731</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>211025</t>
+          <t>211574</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>913455</t>
+          <t>917657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1025358</t>
+          <t>1024029</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1037651</t>
+          <t>1035693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1155967</t>
+          <t>1148130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1982149</t>
+          <t>1986461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2144756</t>
+          <t>2142806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>488903</t>
+          <t>492038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>580562</t>
+          <t>577072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>473334</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561205</t>
+          <t>562513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1108322</t>
+          <t>1118529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>447819</t>
+          <t>447560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>499888</t>
+          <t>499714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>515695</t>
+          <t>515649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>579768</t>
+          <t>577886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>984006</t>
+          <t>981302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1062750</t>
+          <t>1058754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29859</t>
+          <t>29166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>51638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>60595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89802</t>
+          <t>90618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>80345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127587</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83873</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127056</t>
+          <t>126707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177919</t>
+          <t>179685</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240768</t>
+          <t>242277</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34777</t>
+          <t>34157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48077</t>
+          <t>47854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73702</t>
+          <t>75430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324759</t>
+          <t>276119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>777153</t>
+          <t>776659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>632901</t>
+          <t>635246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>681954</t>
+          <t>686493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>851744</t>
+          <t>827459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1439605</t>
+          <t>1443252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>27636</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80263</t>
+          <t>80884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>80232</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>83233</t>
+          <t>85163</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>149692</t>
+          <t>151825</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230887</t>
+          <t>230800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>783289</t>
+          <t>845713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130276</t>
+          <t>128467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171443</t>
+          <t>169102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>373304</t>
+          <t>372655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1081866</t>
+          <t>1127849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124722</t>
+          <t>127443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68141</t>
+          <t>66805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99484</t>
+          <t>98985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118814</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210789</t>
+          <t>211017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>426904</t>
+          <t>430890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>482617</t>
+          <t>486101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>609740</t>
+          <t>610994</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>805547</t>
+          <t>806780</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1060719</t>
+          <t>1060899</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1322795</t>
+          <t>1340357</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22126</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49512</t>
+          <t>48916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73714</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88305</t>
+          <t>87363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90968</t>
+          <t>90319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88593</t>
+          <t>90074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165883</t>
+          <t>166248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119308</t>
+          <t>121475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>172083</t>
+          <t>169754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78875</t>
+          <t>80388</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>204132</t>
+          <t>205487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191012</t>
+          <t>185888</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>350306</t>
+          <t>352260</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>483710</t>
+          <t>480760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>549554</t>
+          <t>546358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>467214</t>
+          <t>473509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>636019</t>
+          <t>637291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>975088</t>
+          <t>981758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1163908</t>
+          <t>1169347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62446</t>
+          <t>63395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102534</t>
+          <t>104744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>67632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>103193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139494</t>
+          <t>140855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194894</t>
+          <t>194829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195928</t>
+          <t>196332</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252918</t>
+          <t>252193</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189689</t>
+          <t>195794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>276973</t>
+          <t>277763</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>419913</t>
+          <t>416645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>512956</t>
+          <t>513760</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -7463,12 +7463,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84097</t>
+          <t>81936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126842</t>
+          <t>127160</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104645</t>
+          <t>104853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>389518</t>
+          <t>358729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>204960</t>
+          <t>201445</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>488650</t>
+          <t>473298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1562695</t>
+          <t>1609846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2236086</t>
+          <t>2234310</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2330217</t>
+          <t>2339580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2672409</t>
+          <t>2679549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4041784</t>
+          <t>3973335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4782236</t>
+          <t>4786039</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>156025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>238211</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176683</t>
+          <t>175549</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>247518</t>
+          <t>242422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>359613</t>
+          <t>357292</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>465817</t>
+          <t>466268</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>615159</t>
+          <t>616833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1480020</t>
+          <t>1457534</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>462986</t>
+          <t>462330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>626384</t>
+          <t>621803</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1172093</t>
+          <t>1155383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2185682</t>
+          <t>2117910</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>276342</t>
+          <t>287278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>413108</t>
+          <t>412953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363645</t>
+          <t>358684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>641776</t>
+          <t>652698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7969,47 +7969,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>805297</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>703072</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1014943</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>9,82%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>805297</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>703057</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1011512</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D$aparatos-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>456935</t>
+          <t>453322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>505052</t>
+          <t>504085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454358</t>
+          <t>455923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>506555</t>
+          <t>505634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>926495</t>
+          <t>926317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>995012</t>
+          <t>996904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>29514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>25330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45473</t>
+          <t>47529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153609</t>
+          <t>155158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>201865</t>
+          <t>203291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153070</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199119</t>
+          <t>199660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>320983</t>
+          <t>321962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>387663</t>
+          <t>386636</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39266</t>
+          <t>41598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44116</t>
+          <t>42095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44250</t>
+          <t>45202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76089</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>640038</t>
+          <t>635139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>702082</t>
+          <t>700682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>668838</t>
+          <t>674062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>731756</t>
+          <t>734142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1332836</t>
+          <t>1326213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1420802</t>
+          <t>1416196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49548</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>23954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50124</t>
+          <t>48858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>55548</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91303</t>
+          <t>90757</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>250790</t>
+          <t>250042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>308622</t>
+          <t>308538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231993</t>
+          <t>234026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>288483</t>
+          <t>291316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>494750</t>
+          <t>503020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>581371</t>
+          <t>585879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>45261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44892</t>
+          <t>46541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>47620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80556</t>
+          <t>80094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>476954</t>
+          <t>477875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>531972</t>
+          <t>533041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>535024</t>
+          <t>531501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>585855</t>
+          <t>584868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1027207</t>
+          <t>1023208</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1102251</t>
+          <t>1100293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>162541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215232</t>
+          <t>213553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144507</t>
+          <t>147800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192331</t>
+          <t>196856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>325612</t>
+          <t>324841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395221</t>
+          <t>392319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76551</t>
+          <t>73918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57706</t>
+          <t>59162</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79567</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120776</t>
+          <t>120891</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>474538</t>
+          <t>474346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>534618</t>
+          <t>536921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>534351</t>
+          <t>532869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>598518</t>
+          <t>601845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1031255</t>
+          <t>1025524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1122764</t>
+          <t>1115335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>61496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>29126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71112</t>
+          <t>70888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107897</t>
+          <t>105220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>343509</t>
+          <t>342099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>405238</t>
+          <t>402221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>365785</t>
+          <t>366636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>429888</t>
+          <t>431965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>724989</t>
+          <t>726152</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>815516</t>
+          <t>811360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71555</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64998</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>102932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2104221</t>
+          <t>2095498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2220822</t>
+          <t>2220617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2252736</t>
+          <t>2254162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2368984</t>
+          <t>2370938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4389541</t>
+          <t>4389925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4560390</t>
+          <t>4545185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>86186</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130727</t>
+          <t>129469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76675</t>
+          <t>75749</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>116826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>177222</t>
+          <t>177480</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>234637</t>
+          <t>238128</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>961210</t>
+          <t>962831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1074530</t>
+          <t>1073187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>953120</t>
+          <t>951445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1056955</t>
+          <t>1055961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1944460</t>
+          <t>1950028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2096331</t>
+          <t>2105918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117374</t>
+          <t>121144</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166824</t>
+          <t>170593</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135924</t>
+          <t>135416</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184531</t>
+          <t>186417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266958</t>
+          <t>268301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>339356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>341424</t>
+          <t>339562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392956</t>
+          <t>392247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>348335</t>
+          <t>346331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>399230</t>
+          <t>400247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>703775</t>
+          <t>704897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>777360</t>
+          <t>777416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24823</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>33697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153765</t>
+          <t>154312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200644</t>
+          <t>199522</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145216</t>
+          <t>148115</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189330</t>
+          <t>192613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>313275</t>
+          <t>310002</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>378484</t>
+          <t>377709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103879</t>
+          <t>104231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145631</t>
+          <t>146816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96742</t>
+          <t>94893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134848</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>211457</t>
+          <t>214654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>267855</t>
+          <t>268621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>547247</t>
+          <t>551565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>613713</t>
+          <t>610039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>555447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>627793</t>
+          <t>619650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1123973</t>
+          <t>1121530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1220698</t>
+          <t>1217736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>249542</t>
+          <t>250133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>310193</t>
+          <t>307474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>273018</t>
+          <t>273137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>331400</t>
+          <t>331721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>536808</t>
+          <t>536482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>624469</t>
+          <t>622047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128412</t>
+          <t>128652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176575</t>
+          <t>176391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121947</t>
+          <t>122457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167439</t>
+          <t>167179</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263652</t>
+          <t>262222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329692</t>
+          <t>327453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>296195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>351872</t>
+          <t>352889</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>295737</t>
+          <t>297356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>352006</t>
+          <t>354435</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611505</t>
+          <t>612936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>696488</t>
+          <t>694321</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25263</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>43056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235915</t>
+          <t>235418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289304</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>269339</t>
+          <t>265748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323206</t>
+          <t>322123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>518243</t>
+          <t>520683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596674</t>
+          <t>599791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134562</t>
+          <t>132994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>181188</t>
+          <t>179289</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132408</t>
+          <t>130280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>179656</t>
+          <t>175549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>276711</t>
+          <t>276585</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347597</t>
+          <t>342044</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>498689</t>
+          <t>497734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>557323</t>
+          <t>562079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>528911</t>
+          <t>534198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>598806</t>
+          <t>600048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1048233</t>
+          <t>1045001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1142084</t>
+          <t>1137933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73501</t>
+          <t>72201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34904</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>85509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127974</t>
+          <t>125246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225191</t>
+          <t>224339</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280113</t>
+          <t>279896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>300890</t>
+          <t>297382</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>364132</t>
+          <t>360425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>539956</t>
+          <t>541461</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>627982</t>
+          <t>625433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82254</t>
+          <t>80896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122508</t>
+          <t>121613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123730</t>
+          <t>125338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178325</t>
+          <t>174553</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235450</t>
+          <t>234654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1741456</t>
+          <t>1742589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1860158</t>
+          <t>1859574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1789234</t>
+          <t>1791631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1913164</t>
+          <t>1914126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3571319</t>
+          <t>3566002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3737823</t>
+          <t>3733767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>77926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>116207</t>
+          <t>115937</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>71198</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>156731</t>
+          <t>157320</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>211574</t>
+          <t>213105</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>917657</t>
+          <t>916057</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1024029</t>
+          <t>1026634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1035693</t>
+          <t>1041940</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1148130</t>
+          <t>1158477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1986461</t>
+          <t>1984874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2142806</t>
+          <t>2142094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>492038</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577072</t>
+          <t>577793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>476803</t>
+          <t>472346</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>562513</t>
+          <t>560787</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>986040</t>
+          <t>995617</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1118529</t>
+          <t>1107542</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>476371</t>
+          <t>514473</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>447560</t>
+          <t>487540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>499714</t>
+          <t>540061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>540264</t>
+          <t>534808</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>515649</t>
+          <t>512157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>577886</t>
+          <t>556773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1016635</t>
+          <t>1049281</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>981302</t>
+          <t>1016181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1058754</t>
+          <t>1082115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>33881</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>45403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5899,32 +5899,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40469</t>
+          <t>41698</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29166</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>74401</t>
+          <t>75579</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60595</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90618</t>
+          <t>91690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -5977,32 +5977,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99928</t>
+          <t>107877</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80345</t>
+          <t>86112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131755</t>
+          <t>134038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108142</t>
+          <t>114561</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82828</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126707</t>
+          <t>131378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>208070</t>
+          <t>222438</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>179685</t>
+          <t>196752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>242277</t>
+          <t>252876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6090,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>23209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>46615</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6125,32 +6125,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>32488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47854</t>
+          <t>54255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6160,32 +6160,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75430</t>
+          <t>92573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6207,32 +6207,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>607653</t>
+          <t>676812</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276119</t>
+          <t>643189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>776659</t>
+          <t>717019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6242,32 +6242,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>660405</t>
+          <t>742138</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>635246</t>
+          <t>713008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>686493</t>
+          <t>767552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1268057</t>
+          <t>1418950</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827459</t>
+          <t>1369026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1443252</t>
+          <t>1462177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56992</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27636</t>
+          <t>41703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80884</t>
+          <t>70482</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>67717</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>55540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80232</t>
+          <t>83041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>122689</t>
+          <t>122310</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85163</t>
+          <t>103338</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>151825</t>
+          <t>144106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>436687</t>
+          <t>207444</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230800</t>
+          <t>177382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>845713</t>
+          <t>238005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6468,32 +6468,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147464</t>
+          <t>160870</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128467</t>
+          <t>140226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169102</t>
+          <t>183505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>584152</t>
+          <t>368314</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372655</t>
+          <t>334269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1127849</t>
+          <t>408687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -6546,32 +6546,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>108914</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45042</t>
+          <t>88469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127443</t>
+          <t>134978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6581,32 +6581,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>97262</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66805</t>
+          <t>81231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98985</t>
+          <t>115633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6616,32 +6616,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>173280</t>
+          <t>206177</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111307</t>
+          <t>179720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211017</t>
+          <t>243251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -6663,32 +6663,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>457039</t>
+          <t>501185</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>430890</t>
+          <t>469217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486101</t>
+          <t>531181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6698,32 +6698,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>690650</t>
+          <t>511529</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>610994</t>
+          <t>487999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>806780</t>
+          <t>536690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1147689</t>
+          <t>1012715</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1060899</t>
+          <t>973052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1340357</t>
+          <t>1054344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6776,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21969</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>55545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>52255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -6889,67 +6889,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70294</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54428</t>
+          <t>61820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87363</t>
+          <t>101635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>76152</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>62675</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>91549</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>65178</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33923</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>90319</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>135471</t>
+          <t>157021</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>136073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166248</t>
+          <t>181250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -7002,32 +7002,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
+          <t>175492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121475</t>
+          <t>150347</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169754</t>
+          <t>206229</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7037,32 +7037,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>152583</t>
+          <t>194190</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>80388</t>
+          <t>171806</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>205487</t>
+          <t>216599</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7072,32 +7072,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>296526</t>
+          <t>369683</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>185888</t>
+          <t>333201</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>352260</t>
+          <t>404018</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>517857</t>
+          <t>559963</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>480760</t>
+          <t>523230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>546358</t>
+          <t>592873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>586344</t>
+          <t>634723</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>473509</t>
+          <t>603466</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>637291</t>
+          <t>661180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1104201</t>
+          <t>1194686</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>981758</t>
+          <t>1150547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1169347</t>
+          <t>1239354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80245</t>
+          <t>78397</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>63346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104744</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85782</t>
+          <t>90592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>75679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103193</t>
+          <t>106495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>166027</t>
+          <t>168989</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140855</t>
+          <t>147545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194829</t>
+          <t>192430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>222798</t>
+          <t>232001</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196332</t>
+          <t>202523</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252193</t>
+          <t>260813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>247155</t>
+          <t>268443</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>195794</t>
+          <t>241240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>277763</t>
+          <t>296905</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>469953</t>
+          <t>500444</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>416645</t>
+          <t>465638</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>513760</t>
+          <t>539454</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -7458,32 +7458,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
+          <t>117561</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81936</t>
+          <t>95084</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127160</t>
+          <t>141320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7493,32 +7493,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>172658</t>
+          <t>122233</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104853</t>
+          <t>105536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>358729</t>
+          <t>144404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7528,32 +7528,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>276519</t>
+          <t>239793</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>201445</t>
+          <t>211141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>473298</t>
+          <t>271961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1609846</t>
+          <t>2191626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2234310</t>
+          <t>2316949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2339580</t>
+          <t>2370189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2679549</t>
+          <t>2474243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3973335</t>
+          <t>4598997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4786039</t>
+          <t>4761793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>203541</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156025</t>
+          <t>181171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240011</t>
+          <t>236711</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>175549</t>
+          <t>202710</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>242422</t>
+          <t>254958</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>418488</t>
+          <t>435368</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>357292</t>
+          <t>396060</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>466268</t>
+          <t>475223</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>829707</t>
+          <t>628191</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>616833</t>
+          <t>580015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1457534</t>
+          <t>684328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>567939</t>
+          <t>620026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>462330</t>
+          <t>579647</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621803</t>
+          <t>664506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1397646</t>
+          <t>1248217</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1155383</t>
+          <t>1185152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2117910</t>
+          <t>1315414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -7914,32 +7914,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>287278</t>
+          <t>390405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>412953</t>
+          <t>476922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7949,32 +7949,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>358684</t>
+          <t>422255</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>652698</t>
+          <t>496250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7984,32 +7984,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>703072</t>
+          <t>834312</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1014943</t>
+          <t>949008</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
